--- a/employee_surveys/032_employee_relationship_dynamics_survey--employee_surveys.xlsx
+++ b/employee_surveys/032_employee_relationship_dynamics_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Manager Name</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Direct Report</t>
+          <t>Direct Report Name</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Manager Email</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Manager Phone</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
